--- a/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.49%349,000</t>
+          <t>8.51%349,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.51%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.98%519,000</t>
+          <t>6.25%531,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.98%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>519000</v>
+        <v>531000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,33 +692,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3510</v>
+        <v>3440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.53%164,000</t>
+          <t>5.74%169,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>164000</v>
+        <v>169000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.21%66,000</t>
+          <t>5.05%66,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.05%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.89%101,000</t>
+          <t>4.86%101,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2110</v>
+        <v>1050</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.41%215,191</t>
+          <t>4.30%440,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>215191</v>
+        <v>440000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.12%82,000</t>
+          <t>3.99%82,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1010</v>
+        <v>2085</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.10%431,000</t>
+          <t>3.99%195,191</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>431000</v>
+        <v>195191</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.79%20,600</t>
+          <t>3.80%20,600</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1420</v>
+        <v>1460</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.34%254,000</t>
+          <t>3.49%254,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.21%630,000</t>
+          <t>3.15%626,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>630000</v>
+        <v>626000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.94%1,938,000</t>
+          <t>3.03%1,938,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>3.03%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>11835</v>
+        <v>6800</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.37%20,000</t>
+          <t>2.73%41,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>20000</v>
+        <v>41000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:55</t>
+          <t>2026-10-02 19:06:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,25 +1358,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1535</v>
+        <v>1965</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.37%159,000</t>
+          <t>2.37%129,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1385,11 +1385,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>159000</v>
+        <v>129000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6875</v>
+        <v>1535</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.27%34,000</t>
+          <t>2.36%159,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>34000</v>
+        <v>159000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1900</v>
+        <v>12145</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.25%129,000</t>
+          <t>2.29%20,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>129000</v>
+        <v>20000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.28%180</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>180</v>
+        <v>626</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.18%1,238,000</t>
+          <t>2.26%388,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1238000</v>
+        <v>388000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.56%179</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2555</v>
+        <v>179</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.11%83,000</t>
+          <t>2.12%1,214,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>83000</v>
+        <v>1214000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>602</v>
+        <v>2540</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.09%388,000</t>
+          <t>2.05%83,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>388000</v>
+        <v>83000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.00%108,000</t>
+          <t>1.99%108,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.09%546</t>
+          <t>+6.23%580</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>+6.23%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>546</v>
+        <v>580</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.88%348,000</t>
+          <t>1.84%348,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6205</v>
+        <v>6290</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.52%26,000</t>
+          <t>1.56%26,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,33 +1912,33 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.43%571,000</t>
+          <t>1.36%553,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>571000</v>
+        <v>553000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,33 +1973,33 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.59%510</t>
+          <t>+10%561</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.59%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>510</v>
+        <v>561</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.27%255,000</t>
+          <t>1.21%246,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>255000</v>
+        <v>246000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,33 +2034,33 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.84%1000</t>
+          <t>+1.5%1015</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.84%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.00%106,000</t>
+          <t>1.07%111,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>106000</v>
+        <v>111000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.41%723</t>
+          <t>+6.39%683</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+6.39%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>723</v>
+        <v>683</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.60%84,000</t>
+          <t>0.65%105,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>84000</v>
+        <v>105000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2006東和鋼鐵</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.94%84.6</t>
+          <t>-0.97%716</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>84.59999999999999</v>
+        <v>716</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.59%699,000</t>
+          <t>0.63%90,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>699000</v>
+        <v>90000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,33 +2217,33 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.59%85,000</t>
+          <t>0.62%90,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>85000</v>
+        <v>90000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:57</t>
+          <t>2026-10-02 19:06:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3324雙鴻</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.02%505</t>
+          <t>-0.33%1525</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.02%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>505</v>
+        <v>1525</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.59%121,000</t>
+          <t>0.61%41,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>121000</v>
+        <v>41000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2006東和鋼鐵</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.05%642</t>
+          <t>+2.36%86.6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>642</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.58%95,000</t>
+          <t>0.57%699,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>95000</v>
+        <v>699000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3324雙鴻</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.33%1525</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1525</v>
+        <v>2310</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.57%38,000</t>
+          <t>0.51%22,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>38000</v>
+        <v>22000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>+0.34%146</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2390</v>
+        <v>146</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.53%22,000</t>
+          <t>0.50%357,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>22000</v>
+        <v>357000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.39%145.5</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>145.5</v>
+        <v>2660</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.50%357,000</t>
+          <t>0.49%19,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>357000</v>
+        <v>19000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2347聯強</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>+1.78%97.1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2660</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.50%19,000</t>
+          <t>0.44%474,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>19000</v>
+        <v>474000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>3532台勝科</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.53%95.4</t>
+          <t>+0.32%475.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>95.40000000000001</v>
+        <v>475.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.44%474,000</t>
+          <t>0.37%80,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>474000</v>
+        <v>80000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3532台勝科</t>
+          <t>2606裕民</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.64%474</t>
+          <t>+3.27%75.9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>474</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%80,000</t>
+          <t>0.35%498,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>80000</v>
+        <v>498000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2606裕民</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.14%73.5</t>
+          <t>+6.16%100</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>73.5</v>
+        <v>100</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.36%498,000</t>
+          <t>0.34%378,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>498000</v>
+        <v>378000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.19%94.2</t>
+          <t>+0.84%240</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.19%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>94.2</v>
+        <v>240</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.36%378,000</t>
+          <t>0.31%135,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>378000</v>
+        <v>135000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.63%238</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>238</v>
+        <v>2190</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.32%135,000</t>
+          <t>0.30%15,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>135000</v>
+        <v>15000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>+1.16%961</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2080</v>
+        <v>961</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.31%15,000</t>
+          <t>0.30%33,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>15000</v>
+        <v>33000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3406玉晶光</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+6.74%950</t>
+          <t>+2.46%542</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+6.74%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>950</v>
+        <v>542</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.29%33,000</t>
+          <t>0.28%54,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>33000</v>
+        <v>54000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.76%529</t>
+          <t>+0.95%106</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>529</v>
+        <v>106</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.28%54,000</t>
+          <t>0.27%266,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>54000</v>
+        <v>266000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.45%105</t>
+          <t>-1.05%281.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.45%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>105</v>
+        <v>281.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.27%266,000</t>
+          <t>0.25%89,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>266000</v>
+        <v>89000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:58</t>
+          <t>2026-10-02 19:06:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.79%284.5</t>
+          <t>+7.64%225.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+7.64%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>284.5</v>
+        <v>225.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.24%89,000</t>
+          <t>0.25%113,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>89000</v>
+        <v>113000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.88%224.5</t>
+          <t>+0.67%226</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>224.5</v>
+        <v>226</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+7.64%225.5</t>
+          <t>0%48.05</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+7.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>225.5</v>
+        <v>48.05</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.23%113,000</t>
+          <t>0.21%459,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>113000</v>
+        <v>459000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>2618長榮航</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.26%48.05</t>
+          <t>+0.36%42.35</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>48.05</v>
+        <v>42.35</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.21%459,000</t>
+          <t>0.20%487,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>459000</v>
+        <v>487000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.21%10,000</t>
+          <t>0.20%10,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,34 +3493,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2618長榮航</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.52%42.2</t>
+          <t>-0.67%1490</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>42.2</v>
+        <v>1490</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.20%487,000</t>
+          <t>0.16%11,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>487000</v>
+        <v>11000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 00:27:59</t>
+          <t>2026-10-02 19:06:31</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,163 +3554,41 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-0.67%1490</t>
+          <t>0%1290</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.16%11,000</t>
+          <t>0.02%1,873</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>11000</v>
+        <v>1873</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:27:59</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2885元大金</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-1.61%67.4</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-1.61%</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.07%105,360</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>0.07%</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>105360</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-0.00%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-10-02 00:27:59</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>5289宜鼎</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>0%1290</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>1290</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>0.04%2,872</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>0.04%</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>2872</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:27</t>
+          <t>2026-10-02 22:51:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:29</t>
+          <t>2026-10-02 22:51:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:30</t>
+          <t>2026-10-02 22:51:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 19:06:31</t>
+          <t>2026-10-02 22:51:04</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:00</t>
+          <t>2026-10-02 23:00:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:02</t>
+          <t>2026-10-02 23:00:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:03</t>
+          <t>2026-10-02 23:00:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 22:51:04</t>
+          <t>2026-10-02 23:00:11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:07</t>
+          <t>2026-10-02 23:49:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:09</t>
+          <t>2026-10-02 23:49:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:10</t>
+          <t>2026-10-02 23:49:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-02 23:00:11</t>
+          <t>2026-10-02 23:49:21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
